--- a/Nhom01/SE_9/SE_9_Nhom01_VisionaryScenario.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_VisionaryScenario.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Each step names actor, system support and benefit, and is a business flow rather than a user story.</t>
+          <t>Mỗi bước tương lai nêu ai thực hiện, hệ thống hỗ trợ gì và lợi ích; nội dung được viết thành luồng nghiệp vụ, không viết theo mẫu câu chuyện người dùng.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–12, A:F</t>
+          <t>VS-001–VS-009</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Version 1.0 covers households/residents, fee catalog, collection, search/statistics and login/password change.</t>
+          <t>Phiên bản 1.0 bao gồm hộ gia đình và cư dân, danh mục phí, thu phí, tra cứu và thống kê, đăng nhập và đổi mật khẩu.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>VS-001…VS-009</t>
+          <t>VS-001–VS-009</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Version 2.0 only indicates parking and collection of electricity, water and internet charges.</t>
+          <t>Phiên bản 2.0 chỉ định hướng các khoản phí gửi xe và việc thu hộ tiền điện, nước, Internet.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>VS-003/004</t>
+          <t>VS-003–VS-004; Đề bài – phạm vi phiên bản 2.0</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Every As-Is pain is addressed and every wish appears.</t>
+          <t>Mọi vấn đề hiện trạng đều được xử lý và mọi mong muốn đều xuất hiện trong kịch bản tương lai.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>As-Is AS-001…AS-008; Wish List RAW-001…RAW-012; VS-001…009</t>
+          <t>VS-001–VS-009; AS-001–AS-008; RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>A team-added step is distinguishable from a client wish.</t>
+          <t>Bước do nhóm bổ sung được phân biệt với mong muốn của khách hàng.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–12; không có cột nguồn/origin</t>
+          <t>VS-001–VS-009; RAW-001–RAW-012</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
